--- a/data/zonar/Export.xlsx
+++ b/data/zonar/Export.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Created</t>
   </si>
@@ -25,94 +25,202 @@
     <t>Status</t>
   </si>
   <si>
-    <t>2026-04-09 21:09:15.780</t>
-  </si>
-  <si>
-    <t>11000001,5,6660000170,1,1,1,10,7,1765360674,3.4654168,-76.5259853,251,0,11110001,00000000,OFF,1101011,5,4,501,20185,0x00000000,15984|</t>
-  </si>
-  <si>
-    <t>0x830566600001700101010A0007693944220210C7D8D2630FB300FB008F00D60504000001F500004ED90000000000003E70</t>
-  </si>
-  <si>
-    <t>2026-04-09 21:09:15.921</t>
-  </si>
-  <si>
-    <t>11000001,5,6660000170,1,1,1,10,1,3,0,0,0,0,00001111,00000001,OFF,1101001,6,4,501,19608,0x00000000,15984|</t>
-  </si>
-  <si>
-    <t>0x830566600001700101010A0001000000030000000000000000000000F080960604000001F500004C980000000000003E70</t>
-  </si>
-  <si>
-    <t>2026-04-09 21:18:42.216</t>
-  </si>
-  <si>
-    <t>11000001,5,6660000170,1,1,1,10,2,1775769522,3.4654406,-76.5260943,17,0,01110000,11110000,OFF,1101001,5,4,501,11856,0x00000000,15984|</t>
-  </si>
-  <si>
-    <t>0x830566600001700101010A000269D817B20210C8C6D2630B710011000E0F960504000001F500002E500000000000003E70</t>
-  </si>
-  <si>
-    <t>2026-04-09 21:40:26.173</t>
-  </si>
-  <si>
-    <t>11000001,5,6660000170,1,1,1,10,3,1775770826,3.465383,-76.5259831,197,1,11110000,11110000,ON,1101000,1,4,501,11856,0x00000000,15984|</t>
-  </si>
-  <si>
-    <t>0x830566600001700101010A000369D81CCA0210C686D2630FC900C5010F0F170104000001F500002E500000000000003E70</t>
-  </si>
-  <si>
-    <t>2026-04-09 21:42:02.697</t>
-  </si>
-  <si>
-    <t>11000001,5,6660000170,1,1,1,10,4,1775770923,3.465395,-76.5259938,208,0,11110000,11110000,OFF,1101000,2,4,501,11856,0x00000000,461|</t>
-  </si>
-  <si>
-    <t>0x830566600001700101010A000469D81D2B0210C6FED2630F5E00D0000F0F160204000001F500002E5000000000000001CD</t>
-  </si>
-  <si>
-    <t>2026-04-09 21:46:35.588</t>
-  </si>
-  <si>
-    <t>11000001,5,6660000170,1,1,1,10,5,1775771222,3.4654053,-76.5259745,208,0,11110000,11110000,ON,1101000,1,4,501,11856,0x00000000,458|</t>
-  </si>
-  <si>
-    <t>0x830566600001700101010A000569D81E560210C765D263101F00D0000F0F170104000001F500002E5000000000000001CA</t>
-  </si>
-  <si>
-    <t>2026-04-09 21:50:01.214</t>
-  </si>
-  <si>
-    <t>11000001,5,6660000170,1,1,1,10,6,1775771401,3.4654156,-76.5259893,218,0,11110000,11110000,ON,1101000,4,4,501,11856,0x00000000,457|</t>
-  </si>
-  <si>
-    <t>0x830566600001700101010A000669D81F090210C7CCD2630F8B00DA000F0F170404000001F500002E5000000000000001C9</t>
-  </si>
-  <si>
-    <t>2026-04-09 21:51:34.822</t>
-  </si>
-  <si>
-    <t>11000001,5,6660000170,1,1,1,10,7,1775771521,3.465378,-76.5259873,218,0,11110000,11110000,ON,1101000,45,4,501,11856,0x00000000,455|</t>
-  </si>
-  <si>
-    <t>0x830566600001700101010A000769D81F810210C654D2630F9F00DA000F0F172D04000001F500002E5000000000000001C7</t>
-  </si>
-  <si>
-    <t>2026-04-09 22:37:50.696</t>
-  </si>
-  <si>
-    <t>11000001,5,6660000170,1,1,1,10,8,1775774271,3.4653951,-76.5259566,241,0,01110000,11110000,OFF,1101010,2,4,501,11856,0x00000000,435|</t>
-  </si>
-  <si>
-    <t>0x830566600001700101010A000869D82A3F0210C6FFD26310D200F1000E0F560204000001F500002E5000000000000001B3</t>
-  </si>
-  <si>
-    <t>2026-04-09 22:47:50.168</t>
-  </si>
-  <si>
-    <t>11000001,5,6660000170,1,1,1,10,9,1775774870,3.4653758,-76.5259351,280,0,11110000,11110000,OFF,1101010,5,4,501,11856,0x00000000,15984|</t>
-  </si>
-  <si>
-    <t>0x830566600001700101010A000969D82C960210C63ED26311A90118000F0F560504000001F500002E500000000000003E70</t>
+    <t>2026-04-22 15:27:19.417</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,1,1775687436,0,0,0,0,00000111,00000001,OFF,1101011,6,3,96947572,516,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000169D6D70C0000000000000000000000E080D6060305C74D740000020400000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 15:27:19.593</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,1,2,0,0,0,0,00001111,00000001,OFF,1101000,6,3,96947572,516,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A0001000000020000000000000000000000F08016060305C74D740000020400000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 15:35:22.215</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,2,1776872158,0,0,0,0,00000110,11110001,OFF,1101000,5,3,96947572,25049,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000269E8EADE0000000000000000000000608F16050305C74D74000061D900000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 16:37:29.747</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,3,1776875847,11.1927283,-74.2313956,290,23,00100000,11110000,OFF,1101000,8,3,96947572,24715,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000369E8F94706ABDFF3D3C1301C012217040F16080305C74D740000608B00000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 16:38:01.141</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,4,1776875880,11.1923671,-74.2305208,126,2,11000010,11110000,OFF,1101000,9,3,96947572,24715,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000469E8F96806ABD1D7D3C15248007E02430F16090305C74D740000608B00000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 16:46:13.850</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,5,1776876369,11.1917013,-74.230202,232,11,11000010,11110000,OFF,1101000,8,3,96947572,24685,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000569E8FB5106ABB7D5D3C15EBC00E80B430F16080305C74D740000606D00000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 16:46:48.715</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,6,1776876406,11.1921363,-74.2299876,226,5,00100010,11110000,OFF,1101000,9,3,96947572,24685,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000669E8FB7606ABC8D3D3C1671C00E205440F16090305C74D740000606D00000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 16:55:37.889</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,7,1776876975,11.1930311,-74.2291515,47,22,10100010,11110000,OFF,1101000,8,3,96947572,24685,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000769E8FDAF06ABEBC7D3C187C5002F16450F16080305C74D740000606D00000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 16:56:42.140</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,8,1776877001,11.1928225,-74.2292108,245,3,10100000,11110000,OFF,1101000,9,3,96947572,24685,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000869E8FDC906ABE3A1D3C1857400F503050F16090305C74D740000606D00000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 17:06:43.701</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,9,1776877601,11.1922296,-74.2299625,258,2,10100000,11110000,OFF,1101000,5,3,96947572,24685,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000969E9002106ABCC78D3C16817010202050F16050305C74D740000606D00000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 17:31:42.955</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,10,1776879102,11.194346,-74.2291586,13,16,11000000,11110000,OFF,1101000,8,3,96947572,24685,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000A69E905FE06AC1F24D3C1877E000D10030F16080305C74D740000606D00000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 17:33:08.005</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,11,1776879187,11.1924848,-74.230116,202,3,10100000,11110000,OFF,1101000,9,3,96947572,24685,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000B69E9065306ABD670D3C1621800CA03050F16090305C74D740000606D00000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 17:43:07.942</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,12,1776879787,11.1920463,-74.2299893,194,0,11000000,11110000,OFF,1101000,5,3,96947572,24806,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000C69E908AB06ABC54FD3C1670B00C200030F16050305C74D74000060E600000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 17:44:17.778</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,13,1776879895,11.1922918,-74.229011,79,26,11000010,11110000,OFF,1101000,8,3,96947572,24897,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000D69E9091706ABCEE6D3C18D42004F1A430F16080305C74D740000614100000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 17:45:18.277</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,14,1776879918,11.1921503,-74.2298113,244,1,01100000,11110000,OFF,1101000,9,3,96947572,24897,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000E69E9092E06ABC95FD3C16DFF00F401060F16090305C74D740000614100000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 17:54:40.777</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,15,1776880518,11.1919476,-74.229986,202,7,00100000,11110000,OFF,1101000,5,3,96947572,24897,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A000F69E90B8606ABC174D3C1672C00CA07040F16050305C74D740000614100000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 18:42:20.186</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,16,1776883379,11.1922625,-74.229856,57,0,11010000,11110000,ON,1101000,1,3,96947572,24776,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A001069E916B306ABCDC1D3C16C400039000B0F17010305C74D74000060C800000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 18:46:00.464</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,17,1776883559,11.1922455,-74.2298625,57,0,00110000,11110000,ON,1101000,4,3,96947572,24593,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A001169E9176706ABCD17D3C16BFF0039000C0F17040305C74D740000601100000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 18:46:46.581</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,18,1776883646,11.1922675,-74.2298663,57,0,11010000,11110000,OFF,1101000,2,3,96947572,24745,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A001269E917BE06ABCDF3D3C16BD90039000B0F16020305C74D74000060A900000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 18:49:02.457</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,19,1776883744,11.1922785,-74.229852,57,0,00110000,11110000,ON,1101000,1,3,96947572,24654,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A001369E9182006ABCE61D3C16C680039000C0F17010305C74D740000604E00000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 18:51:23.964</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,20,1776883923,11.1923041,-74.2298465,225,0,10110000,11110000,ON,1101000,4,3,96947581,24563,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A001469E918D306ABCF61D3C16C9F00E1000D0F17040305C74D7D00005FF300000000</t>
+  </si>
+  <si>
+    <t>2026-04-22 18:53:23.762</t>
+  </si>
+  <si>
+    <t>11000001,5,4764383826,1,1,1,10,21,1776884043,11.1922928,-74.2298731,225,0,10110000,11110000,ON,1101000,45,3,96947581,24563,0x00000000,0,0|</t>
+  </si>
+  <si>
+    <t>0x830547643838260101010A001569E9194B06ABCEF0D3C16B9500E1000D0F172D0305C74D7D00005FF300000000</t>
   </si>
 </sst>
 </file>
@@ -304,6 +412,138 @@
         <v>32</v>
       </c>
     </row>
+    <row r="12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
